--- a/UPME_AutoCarga/El_Papá.xlsx
+++ b/UPME_AutoCarga/El_Papá.xlsx
@@ -1441,7 +1441,7 @@
     <t>https://drive.google.com/drive/folders/16DfZviR3HK2rweX-OL9dVN7BhLUkxsmx</t>
   </si>
   <si>
-    <t>P00149</t>
+    <t>P00163</t>
   </si>
   <si>
     <t>L047</t>
